--- a/examples/output/LC2_swissmetro.xlsx
+++ b/examples/output/LC2_swissmetro.xlsx
@@ -507,25 +507,25 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>-0.26941689163151544</v>
+        <v>-0.03592001197000946</v>
       </c>
       <c r="C2">
-        <v>0.11698020358731417</v>
+        <v>0.057925373230071395</v>
       </c>
       <c r="D2">
-        <v>-2.3030981599414155</v>
+        <v>-0.6201084251514488</v>
       </c>
       <c r="E2">
-        <v>0.021273320822156938</v>
+        <v>0.5351864056957825</v>
       </c>
       <c r="F2">
-        <v>0.30415856930686325</v>
+        <v>0.11251491975144849</v>
       </c>
       <c r="G2">
-        <v>-0.8857777449620458</v>
+        <v>-0.31924665679323866</v>
       </c>
       <c r="H2">
-        <v>0.37573730455959753</v>
+        <v>0.7495394794840249</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -533,25 +533,25 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>-0.03591941678676716</v>
+        <v>-0.26941917831260925</v>
       </c>
       <c r="C3">
-        <v>0.057925400417446996</v>
+        <v>0.11698010391633129</v>
       </c>
       <c r="D3">
-        <v>-0.6200978591068714</v>
+        <v>-2.3031196698654695</v>
       </c>
       <c r="E3">
-        <v>0.5351933615957218</v>
+        <v>0.021272110885845574</v>
       </c>
       <c r="F3">
-        <v>0.11251504278867516</v>
+        <v>0.30415805872524493</v>
       </c>
       <c r="G3">
-        <v>-0.31924101788087766</v>
+        <v>-0.8857867499607619</v>
       </c>
       <c r="H3">
-        <v>0.7495437551571094</v>
+        <v>0.3757324511406781</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -611,25 +611,25 @@
         <v>12</v>
       </c>
       <c r="B6">
-        <v>0.48341885129890183</v>
+        <v>-1.8774976628226978</v>
       </c>
       <c r="C6">
-        <v>0.08259257217197545</v>
+        <v>0.12256331783617896</v>
       </c>
       <c r="D6">
-        <v>5.853054803673145</v>
+        <v>-15.318593654034446</v>
       </c>
       <c r="E6">
-        <v>4.826250066258808e-9</v>
+        <v>0.0</v>
       </c>
       <c r="F6">
-        <v>0.1485532742808128</v>
+        <v>0.1751666762470426</v>
       </c>
       <c r="G6">
-        <v>3.2541783655679435</v>
+        <v>-10.718349534558781</v>
       </c>
       <c r="H6">
-        <v>0.0011372085351804007</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -637,25 +637,25 @@
         <v>13</v>
       </c>
       <c r="B7">
-        <v>-1.8774945052484016</v>
+        <v>0.48341577102052685</v>
       </c>
       <c r="C7">
-        <v>0.12256316783019612</v>
+        <v>0.08259248811074442</v>
       </c>
       <c r="D7">
-        <v>-15.31858663974447</v>
+        <v>5.853023465915413</v>
       </c>
       <c r="E7">
-        <v>0.0</v>
+        <v>4.827159783005186e-9</v>
       </c>
       <c r="F7">
-        <v>0.17516646747760192</v>
+        <v>0.14855301820273387</v>
       </c>
       <c r="G7">
-        <v>-10.718344282923168</v>
+        <v>3.254163239960549</v>
       </c>
       <c r="H7">
-        <v>0.0</v>
+        <v>0.0011372690894075888</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -663,22 +663,22 @@
         <v>14</v>
       </c>
       <c r="B8">
-        <v>-1.30125197028047</v>
+        <v>1.301254151741151</v>
       </c>
       <c r="C8">
-        <v>0.09654382823557404</v>
+        <v>0.09654389986313396</v>
       </c>
       <c r="D8">
-        <v>-13.478354795557923</v>
+        <v>13.478367391268447</v>
       </c>
       <c r="E8">
         <v>0.0</v>
       </c>
       <c r="F8">
-        <v>0.1069319558773495</v>
+        <v>0.10693209021433253</v>
       </c>
       <c r="G8">
-        <v>-12.168971937378574</v>
+        <v>12.168977050134748</v>
       </c>
       <c r="H8">
         <v>0.0</v>
@@ -715,25 +715,25 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <v>0.14661337721875484</v>
+        <v>-2.1408815534788608</v>
       </c>
       <c r="C10">
-        <v>0.08874791187733991</v>
+        <v>0.09100107491527075</v>
       </c>
       <c r="D10">
-        <v>1.6520205841168616</v>
+        <v>-23.525893023485626</v>
       </c>
       <c r="E10">
-        <v>0.09853035473148486</v>
+        <v>0.0</v>
       </c>
       <c r="F10">
-        <v>0.15272467999287404</v>
+        <v>0.17053365565730447</v>
       </c>
       <c r="G10">
-        <v>0.9599848382435351</v>
+        <v>-12.554011964541854</v>
       </c>
       <c r="H10">
-        <v>0.3370628457296405</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -741,25 +741,25 @@
         <v>17</v>
       </c>
       <c r="B11">
-        <v>-2.1408811823825356</v>
+        <v>0.1466098602942655</v>
       </c>
       <c r="C11">
-        <v>0.0910010927250876</v>
+        <v>0.08874780273741191</v>
       </c>
       <c r="D11">
-        <v>-23.525884341302284</v>
+        <v>1.6519829874330136</v>
       </c>
       <c r="E11">
-        <v>0.0</v>
+        <v>0.09853801900362047</v>
       </c>
       <c r="F11">
-        <v>0.17053379392565346</v>
+        <v>0.15272419573409968</v>
       </c>
       <c r="G11">
-        <v>-12.553999609695436</v>
+        <v>0.959964854223364</v>
       </c>
       <c r="H11">
-        <v>0.0</v>
+        <v>0.33707290370368725</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -767,25 +767,25 @@
         <v>18</v>
       </c>
       <c r="B12">
-        <v>0.021806441451427124</v>
+        <v>-2.4775406620330105</v>
       </c>
       <c r="C12">
-        <v>0.05664551168653362</v>
+        <v>0.1090980807781439</v>
       </c>
       <c r="D12">
-        <v>0.38496327073714454</v>
+        <v>-22.709296482228744</v>
       </c>
       <c r="E12">
-        <v>0.7002646280463705</v>
+        <v>0.0</v>
       </c>
       <c r="F12">
-        <v>0.06770850181618042</v>
+        <v>0.19954530472336549</v>
       </c>
       <c r="G12">
-        <v>0.32206356464109503</v>
+        <v>-12.415930635239379</v>
       </c>
       <c r="H12">
-        <v>0.7474045400541316</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -793,25 +793,25 @@
         <v>19</v>
       </c>
       <c r="B13">
-        <v>-2.477540868478076</v>
+        <v>0.021807383930342032</v>
       </c>
       <c r="C13">
-        <v>0.10909804092971903</v>
+        <v>0.05664540579283786</v>
       </c>
       <c r="D13">
-        <v>-22.70930666916474</v>
+        <v>0.38498062861612187</v>
       </c>
       <c r="E13">
-        <v>0.0</v>
+        <v>0.7002517676380517</v>
       </c>
       <c r="F13">
-        <v>0.19954517240872635</v>
+        <v>0.06770793233223811</v>
       </c>
       <c r="G13">
-        <v>-12.415939902586839</v>
+        <v>0.32208019325320286</v>
       </c>
       <c r="H13">
-        <v>0.0</v>
+        <v>0.7473919429326712</v>
       </c>
     </row>
   </sheetData>
@@ -829,7 +829,7 @@
         <v>20</v>
       </c>
       <c r="B1">
-        <v>-4318.839822126627</v>
+        <v>-4318.839822128625</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -845,7 +845,7 @@
         <v>22</v>
       </c>
       <c r="B3">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -869,7 +869,7 @@
         <v>26</v>
       </c>
       <c r="B6">
-        <v>1.482623815536499</v>
+        <v>1.3492610454559326</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -893,7 +893,7 @@
         <v>29</v>
       </c>
       <c r="B9">
-        <v>8655.679644253254</v>
+        <v>8655.67964425725</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -901,7 +901,7 @@
         <v>30</v>
       </c>
       <c r="B10">
-        <v>8717.05929236483</v>
+        <v>8717.059292368825</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -909,7 +909,7 @@
         <v>31</v>
       </c>
       <c r="B11">
-        <v>0.3798924894097305</v>
+        <v>0.37989248940944365</v>
       </c>
     </row>
   </sheetData>

--- a/examples/output/LC2_swissmetro.xlsx
+++ b/examples/output/LC2_swissmetro.xlsx
@@ -869,7 +869,7 @@
         <v>26</v>
       </c>
       <c r="B6">
-        <v>1.3492610454559326</v>
+        <v>1.5673589706420898</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/LC2_swissmetro.xlsx
+++ b/examples/output/LC2_swissmetro.xlsx
@@ -869,7 +869,7 @@
         <v>26</v>
       </c>
       <c r="B6">
-        <v>1.5673589706420898</v>
+        <v>1.5855300426483154</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/LC2_swissmetro.xlsx
+++ b/examples/output/LC2_swissmetro.xlsx
@@ -869,7 +869,7 @@
         <v>26</v>
       </c>
       <c r="B6">
-        <v>1.5855300426483154</v>
+        <v>1.4592478275299072</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/LC2_swissmetro.xlsx
+++ b/examples/output/LC2_swissmetro.xlsx
@@ -869,7 +869,7 @@
         <v>26</v>
       </c>
       <c r="B6">
-        <v>1.4592478275299072</v>
+        <v>1.314635992050171</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/LC2_swissmetro.xlsx
+++ b/examples/output/LC2_swissmetro.xlsx
@@ -869,7 +869,7 @@
         <v>26</v>
       </c>
       <c r="B6">
-        <v>1.314635992050171</v>
+        <v>1.4163429737091064</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/LC2_swissmetro.xlsx
+++ b/examples/output/LC2_swissmetro.xlsx
@@ -869,7 +869,7 @@
         <v>26</v>
       </c>
       <c r="B6">
-        <v>1.4163429737091064</v>
+        <v>1.3149337768554688</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/LC2_swissmetro.xlsx
+++ b/examples/output/LC2_swissmetro.xlsx
@@ -869,7 +869,7 @@
         <v>26</v>
       </c>
       <c r="B6">
-        <v>1.3149337768554688</v>
+        <v>1.3474879264831543</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/LC2_swissmetro.xlsx
+++ b/examples/output/LC2_swissmetro.xlsx
@@ -869,7 +869,7 @@
         <v>26</v>
       </c>
       <c r="B6">
-        <v>1.3474879264831543</v>
+        <v>1.3348639011383057</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/LC2_swissmetro.xlsx
+++ b/examples/output/LC2_swissmetro.xlsx
@@ -869,7 +869,7 @@
         <v>26</v>
       </c>
       <c r="B6">
-        <v>1.3348639011383057</v>
+        <v>1.432431936264038</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/LC2_swissmetro.xlsx
+++ b/examples/output/LC2_swissmetro.xlsx
@@ -869,7 +869,7 @@
         <v>26</v>
       </c>
       <c r="B6">
-        <v>1.432431936264038</v>
+        <v>1.3871779441833496</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/LC2_swissmetro.xlsx
+++ b/examples/output/LC2_swissmetro.xlsx
@@ -869,7 +869,7 @@
         <v>26</v>
       </c>
       <c r="B6">
-        <v>1.3871779441833496</v>
+        <v>1.4722650051116943</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/LC2_swissmetro.xlsx
+++ b/examples/output/LC2_swissmetro.xlsx
@@ -507,25 +507,25 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>-0.03592001197000946</v>
+        <v>-0.03592001197000968</v>
       </c>
       <c r="C2">
-        <v>0.057925373230071395</v>
+        <v>0.05792537323007141</v>
       </c>
       <c r="D2">
-        <v>-0.6201084251514488</v>
+        <v>-0.6201084251514524</v>
       </c>
       <c r="E2">
-        <v>0.5351864056957825</v>
+        <v>0.53518640569578</v>
       </c>
       <c r="F2">
-        <v>0.11251491975144849</v>
+        <v>0.11251491975144859</v>
       </c>
       <c r="G2">
-        <v>-0.31924665679323866</v>
+        <v>-0.31924665679324027</v>
       </c>
       <c r="H2">
-        <v>0.7495394794840249</v>
+        <v>0.7495394794840236</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -533,25 +533,25 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>-0.26941917831260925</v>
+        <v>-0.269419178312609</v>
       </c>
       <c r="C3">
-        <v>0.11698010391633129</v>
+        <v>0.1169801039163313</v>
       </c>
       <c r="D3">
-        <v>-2.3031196698654695</v>
+        <v>-2.303119669865467</v>
       </c>
       <c r="E3">
-        <v>0.021272110885845574</v>
+        <v>0.021272110885845796</v>
       </c>
       <c r="F3">
-        <v>0.30415805872524493</v>
+        <v>0.304158058725245</v>
       </c>
       <c r="G3">
-        <v>-0.8857867499607619</v>
+        <v>-0.8857867499607608</v>
       </c>
       <c r="H3">
-        <v>0.3757324511406781</v>
+        <v>0.37573245114067877</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -614,19 +614,19 @@
         <v>-1.8774976628226978</v>
       </c>
       <c r="C6">
-        <v>0.12256331783617896</v>
+        <v>0.12256331783617892</v>
       </c>
       <c r="D6">
-        <v>-15.318593654034446</v>
+        <v>-15.31859365403445</v>
       </c>
       <c r="E6">
         <v>0.0</v>
       </c>
       <c r="F6">
-        <v>0.1751666762470426</v>
+        <v>0.17516667624704257</v>
       </c>
       <c r="G6">
-        <v>-10.718349534558781</v>
+        <v>-10.718349534558783</v>
       </c>
       <c r="H6">
         <v>0.0</v>
@@ -637,22 +637,22 @@
         <v>13</v>
       </c>
       <c r="B7">
-        <v>0.48341577102052685</v>
+        <v>0.48341577102052713</v>
       </c>
       <c r="C7">
-        <v>0.08259248811074442</v>
+        <v>0.0825924881107444</v>
       </c>
       <c r="D7">
-        <v>5.853023465915413</v>
+        <v>5.853023465915418</v>
       </c>
       <c r="E7">
         <v>4.827159783005186e-9</v>
       </c>
       <c r="F7">
-        <v>0.14855301820273387</v>
+        <v>0.1485530182027338</v>
       </c>
       <c r="G7">
-        <v>3.254163239960549</v>
+        <v>3.254163239960552</v>
       </c>
       <c r="H7">
         <v>0.0011372690894075888</v>
@@ -663,22 +663,22 @@
         <v>14</v>
       </c>
       <c r="B8">
-        <v>1.301254151741151</v>
+        <v>1.3012541517411516</v>
       </c>
       <c r="C8">
-        <v>0.09654389986313396</v>
+        <v>0.09654389986313394</v>
       </c>
       <c r="D8">
-        <v>13.478367391268447</v>
+        <v>13.478367391268455</v>
       </c>
       <c r="E8">
         <v>0.0</v>
       </c>
       <c r="F8">
-        <v>0.10693209021433253</v>
+        <v>0.10693209021433252</v>
       </c>
       <c r="G8">
-        <v>12.168977050134748</v>
+        <v>12.168977050134755</v>
       </c>
       <c r="H8">
         <v>0.0</v>
@@ -718,19 +718,19 @@
         <v>-2.1408815534788608</v>
       </c>
       <c r="C10">
-        <v>0.09100107491527075</v>
+        <v>0.09100107491527076</v>
       </c>
       <c r="D10">
-        <v>-23.525893023485626</v>
+        <v>-23.525893023485622</v>
       </c>
       <c r="E10">
         <v>0.0</v>
       </c>
       <c r="F10">
-        <v>0.17053365565730447</v>
+        <v>0.1705336556573045</v>
       </c>
       <c r="G10">
-        <v>-12.554011964541854</v>
+        <v>-12.554011964541852</v>
       </c>
       <c r="H10">
         <v>0.0</v>
@@ -744,22 +744,22 @@
         <v>0.1466098602942655</v>
       </c>
       <c r="C11">
-        <v>0.08874780273741191</v>
+        <v>0.08874780273741194</v>
       </c>
       <c r="D11">
-        <v>1.6519829874330136</v>
+        <v>1.6519829874330132</v>
       </c>
       <c r="E11">
         <v>0.09853801900362047</v>
       </c>
       <c r="F11">
-        <v>0.15272419573409968</v>
+        <v>0.15272419573409976</v>
       </c>
       <c r="G11">
-        <v>0.959964854223364</v>
+        <v>0.9599648542233635</v>
       </c>
       <c r="H11">
-        <v>0.33707290370368725</v>
+        <v>0.3370729037036875</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -767,22 +767,22 @@
         <v>18</v>
       </c>
       <c r="B12">
-        <v>-2.4775406620330105</v>
+        <v>-2.47754066203301</v>
       </c>
       <c r="C12">
         <v>0.1090980807781439</v>
       </c>
       <c r="D12">
-        <v>-22.709296482228744</v>
+        <v>-22.70929648222874</v>
       </c>
       <c r="E12">
         <v>0.0</v>
       </c>
       <c r="F12">
-        <v>0.19954530472336549</v>
+        <v>0.1995453047233654</v>
       </c>
       <c r="G12">
-        <v>-12.415930635239379</v>
+        <v>-12.41593063523938</v>
       </c>
       <c r="H12">
         <v>0.0</v>
@@ -793,25 +793,25 @@
         <v>19</v>
       </c>
       <c r="B13">
-        <v>0.021807383930342032</v>
+        <v>0.02180738393034188</v>
       </c>
       <c r="C13">
-        <v>0.05664540579283786</v>
+        <v>0.05664540579283788</v>
       </c>
       <c r="D13">
-        <v>0.38498062861612187</v>
+        <v>0.38498062861611904</v>
       </c>
       <c r="E13">
-        <v>0.7002517676380517</v>
+        <v>0.7002517676380537</v>
       </c>
       <c r="F13">
-        <v>0.06770793233223811</v>
+        <v>0.06770793233223821</v>
       </c>
       <c r="G13">
-        <v>0.32208019325320286</v>
+        <v>0.32208019325320014</v>
       </c>
       <c r="H13">
-        <v>0.7473919429326712</v>
+        <v>0.7473919429326732</v>
       </c>
     </row>
   </sheetData>
@@ -869,7 +869,7 @@
         <v>26</v>
       </c>
       <c r="B6">
-        <v>1.4722650051116943</v>
+        <v>1.4225139617919922</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/examples/output/LC2_swissmetro.xlsx
+++ b/examples/output/LC2_swissmetro.xlsx
@@ -869,7 +869,7 @@
         <v>26</v>
       </c>
       <c r="B6">
-        <v>1.4225139617919922</v>
+        <v>1.4432079792022705</v>
       </c>
     </row>
     <row r="7" spans="1:2">
